--- a/mes_north_sea/clean_data/nodes/nodes_test.xlsx
+++ b/mes_north_sea/clean_data/nodes/nodes_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\6574114\PycharmProjects\PyHubProductive\mes_north_sea\clean_data\nodes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CDEB90-D59C-4E3B-B31B-D1FACC0886BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAF1031-B391-4E0B-B8D6-D6AB32BF7075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes_used" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="61">
   <si>
     <t>Node</t>
   </si>
@@ -179,6 +179,51 @@
   </si>
   <si>
     <t>offshore_new</t>
+  </si>
+  <si>
+    <t>UK_L</t>
+  </si>
+  <si>
+    <t>New_Offshore_Farms_2040</t>
+  </si>
+  <si>
+    <t>UK_K</t>
+  </si>
+  <si>
+    <t>UK_J</t>
+  </si>
+  <si>
+    <t>UK_I</t>
+  </si>
+  <si>
+    <t>NO_D</t>
+  </si>
+  <si>
+    <t>NO_C</t>
+  </si>
+  <si>
+    <t>NO_B</t>
+  </si>
+  <si>
+    <t>NO_A</t>
+  </si>
+  <si>
+    <t>NL_G</t>
+  </si>
+  <si>
+    <t>NL_F</t>
+  </si>
+  <si>
+    <t>DK_C</t>
+  </si>
+  <si>
+    <t>DE_I</t>
+  </si>
+  <si>
+    <t>DE_H</t>
+  </si>
+  <si>
+    <t>DE_G</t>
   </si>
 </sst>
 </file>
@@ -497,12 +542,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -519,76 +564,76 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
       </c>
       <c r="C2" t="str">
-        <f t="shared" ref="C2:C39" si="0">LEFT(A2,2)</f>
-        <v>BE</v>
+        <f>LEFT(A2,2)</f>
+        <v>DK</v>
       </c>
       <c r="D2">
-        <v>2.4529999999999998</v>
+        <v>7.6520000000000001</v>
       </c>
       <c r="E2">
-        <v>51.496000000000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>56.326000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>44</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" si="0"/>
-        <v>BE</v>
+        <f>LEFT(A3,2)</f>
+        <v>DK</v>
       </c>
       <c r="D3">
-        <v>2.89</v>
+        <v>7.7460000000000004</v>
       </c>
       <c r="E3">
-        <v>51.612000000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>55.750999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C4" t="str">
-        <f t="shared" si="0"/>
-        <v>BE</v>
+        <f>LEFT(A4,2)</f>
+        <v>DK</v>
       </c>
       <c r="D4">
-        <v>3.056</v>
+        <v>6.6260000000000003</v>
       </c>
       <c r="E4">
-        <v>51.011000000000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>56.265999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="str">
-        <f t="shared" si="0"/>
-        <v>BE</v>
+        <f>LEFT(A5,2)</f>
+        <v>DK</v>
       </c>
       <c r="D5">
-        <v>4.8520000000000003</v>
+        <v>10.051</v>
       </c>
       <c r="E5">
-        <v>50.595999999999997</v>
+        <v>55.959000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -603,13 +648,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4994A1-993F-4B0E-B5C8-90E717560862}">
-  <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -626,7 +671,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -634,7 +679,7 @@
         <v>45</v>
       </c>
       <c r="C2" t="str">
-        <f t="shared" ref="C2:C39" si="0">LEFT(A2,2)</f>
+        <f>LEFT(A2,2)</f>
         <v>BE</v>
       </c>
       <c r="D2">
@@ -644,7 +689,7 @@
         <v>51.496000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -652,7 +697,7 @@
         <v>44</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A3,2)</f>
         <v>BE</v>
       </c>
       <c r="D3">
@@ -662,7 +707,7 @@
         <v>51.612000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -670,7 +715,7 @@
         <v>18</v>
       </c>
       <c r="C4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A4,2)</f>
         <v>BE</v>
       </c>
       <c r="D4">
@@ -680,7 +725,7 @@
         <v>51.011000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -688,7 +733,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A5,2)</f>
         <v>BE</v>
       </c>
       <c r="D5">
@@ -698,7 +743,7 @@
         <v>50.595999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -706,7 +751,7 @@
         <v>45</v>
       </c>
       <c r="C6" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A6,2)</f>
         <v>DE</v>
       </c>
       <c r="D6">
@@ -716,7 +761,7 @@
         <v>54.177</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -724,7 +769,7 @@
         <v>45</v>
       </c>
       <c r="C7" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A7,2)</f>
         <v>DE</v>
       </c>
       <c r="D7">
@@ -734,7 +779,7 @@
         <v>54.66</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -742,7 +787,7 @@
         <v>44</v>
       </c>
       <c r="C8" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A8,2)</f>
         <v>DE</v>
       </c>
       <c r="D8">
@@ -752,7 +797,7 @@
         <v>54.387999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -760,7 +805,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A9,2)</f>
         <v>DE</v>
       </c>
       <c r="D9">
@@ -770,7 +815,7 @@
         <v>54.021999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -778,7 +823,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A10,2)</f>
         <v>DE</v>
       </c>
       <c r="D10">
@@ -788,7 +833,7 @@
         <v>54.453000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -796,7 +841,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A11,2)</f>
         <v>DE</v>
       </c>
       <c r="D11">
@@ -806,513 +851,819 @@
         <v>55.131999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="str">
+        <f>LEFT(A12,2)</f>
+        <v>DE</v>
+      </c>
+      <c r="D12">
+        <v>6.3609999999999998</v>
+      </c>
+      <c r="E12">
+        <v>55.012</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="str">
+        <f>LEFT(A13,2)</f>
+        <v>DE</v>
+      </c>
+      <c r="D13">
+        <v>5.0640000000000001</v>
+      </c>
+      <c r="E13">
+        <v>55.156999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="str">
+        <f>LEFT(A14,2)</f>
+        <v>DE</v>
+      </c>
+      <c r="D14">
+        <v>3.637</v>
+      </c>
+      <c r="E14">
+        <v>55.784999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="str">
-        <f t="shared" si="0"/>
-        <v>DE</v>
-      </c>
-      <c r="D12">
-        <v>6.9630000000000001</v>
-      </c>
-      <c r="E12">
-        <v>51.387</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="str">
-        <f t="shared" si="0"/>
-        <v>DE</v>
-      </c>
-      <c r="D13">
-        <v>7.8</v>
-      </c>
-      <c r="E13">
-        <v>52.947000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="str">
-        <f t="shared" si="0"/>
-        <v>DE</v>
-      </c>
-      <c r="D14">
-        <v>9.8059999999999992</v>
-      </c>
-      <c r="E14">
-        <v>53.68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>1</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
       </c>
       <c r="C15" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A15,2)</f>
         <v>DE</v>
       </c>
       <c r="D15">
-        <v>10.785</v>
+        <v>6.9630000000000001</v>
       </c>
       <c r="E15">
-        <v>50.637</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>51.387</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="C16" t="str">
-        <f t="shared" si="0"/>
-        <v>DK</v>
+        <f>LEFT(A16,2)</f>
+        <v>DE</v>
       </c>
       <c r="D16">
-        <v>7.6520000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="E16">
-        <v>56.326000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>52.947000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C17" t="str">
-        <f t="shared" si="0"/>
-        <v>DK</v>
+        <f>LEFT(A17,2)</f>
+        <v>DE</v>
       </c>
       <c r="D17">
-        <v>7.7460000000000004</v>
+        <v>9.8059999999999992</v>
       </c>
       <c r="E17">
-        <v>55.750999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>53.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
       <c r="C18" t="str">
-        <f t="shared" si="0"/>
-        <v>DK</v>
+        <f>LEFT(A18,2)</f>
+        <v>DE</v>
       </c>
       <c r="D18">
-        <v>10.051</v>
+        <v>10.785</v>
       </c>
       <c r="E18">
-        <v>55.959000000000003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>50.637</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
         <v>45</v>
       </c>
       <c r="C19" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A19,2)</f>
+        <v>DK</v>
+      </c>
+      <c r="D19">
+        <v>7.6520000000000001</v>
+      </c>
+      <c r="E19">
+        <v>56.326000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="str">
+        <f>LEFT(A20,2)</f>
+        <v>DK</v>
+      </c>
+      <c r="D20">
+        <v>7.7460000000000004</v>
+      </c>
+      <c r="E20">
+        <v>55.750999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="str">
+        <f>LEFT(A21,2)</f>
+        <v>DK</v>
+      </c>
+      <c r="D21">
+        <v>6.6260000000000003</v>
+      </c>
+      <c r="E21">
+        <v>56.265999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="str">
+        <f>LEFT(A22,2)</f>
+        <v>DK</v>
+      </c>
+      <c r="D22">
+        <v>10.051</v>
+      </c>
+      <c r="E22">
+        <v>55.959000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="str">
+        <f>LEFT(A23,2)</f>
         <v>NL</v>
       </c>
-      <c r="D19">
+      <c r="D23">
         <v>3.6080000000000001</v>
       </c>
-      <c r="E19">
+      <c r="E23">
         <v>52.927999999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B24" t="s">
         <v>45</v>
       </c>
-      <c r="C20" t="str">
-        <f t="shared" si="0"/>
+      <c r="C24" t="str">
+        <f>LEFT(A24,2)</f>
         <v>NL</v>
       </c>
-      <c r="D20">
+      <c r="D24">
         <v>3.1779999999999999</v>
       </c>
-      <c r="E20">
+      <c r="E24">
         <v>53.1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>40</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B25" t="s">
         <v>44</v>
       </c>
-      <c r="C21" t="str">
-        <f t="shared" si="0"/>
+      <c r="C25" t="str">
+        <f>LEFT(A25,2)</f>
         <v>NL</v>
       </c>
-      <c r="D21">
+      <c r="D25">
         <v>2.99</v>
       </c>
-      <c r="E21">
+      <c r="E25">
         <v>51.698</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>39</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B26" t="s">
         <v>44</v>
       </c>
-      <c r="C22" t="str">
-        <f t="shared" si="0"/>
+      <c r="C26" t="str">
+        <f>LEFT(A26,2)</f>
         <v>NL</v>
       </c>
-      <c r="D22">
+      <c r="D26">
         <v>4.01</v>
       </c>
-      <c r="E22">
+      <c r="E26">
         <v>52.518999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B27" t="s">
         <v>44</v>
       </c>
-      <c r="C23" t="str">
-        <f t="shared" si="0"/>
+      <c r="C27" t="str">
+        <f>LEFT(A27,2)</f>
         <v>NL</v>
       </c>
-      <c r="D23">
+      <c r="D27">
         <v>5.9640000000000004</v>
       </c>
-      <c r="E23">
+      <c r="E27">
         <v>54.036000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" t="str">
+        <f>LEFT(A28,2)</f>
+        <v>NL</v>
+      </c>
+      <c r="D28">
+        <v>3.9359999999999999</v>
+      </c>
+      <c r="E28">
+        <v>53.177999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="str">
+        <f>LEFT(A29,2)</f>
+        <v>NL</v>
+      </c>
+      <c r="D29">
+        <v>5.6420000000000003</v>
+      </c>
+      <c r="E29">
+        <v>54.021000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>10</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B30" t="s">
         <v>18</v>
       </c>
-      <c r="C24" t="str">
-        <f t="shared" si="0"/>
+      <c r="C30" t="str">
+        <f>LEFT(A30,2)</f>
         <v>NL</v>
       </c>
-      <c r="D24">
+      <c r="D30">
         <v>4.2439999999999998</v>
       </c>
-      <c r="E24">
+      <c r="E30">
         <v>51.761000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>9</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B31" t="s">
         <v>18</v>
       </c>
-      <c r="C25" t="str">
-        <f t="shared" si="0"/>
+      <c r="C31" t="str">
+        <f>LEFT(A31,2)</f>
         <v>NL</v>
       </c>
-      <c r="D25">
+      <c r="D31">
         <v>4.9950000000000001</v>
       </c>
-      <c r="E25">
+      <c r="E31">
         <v>52.45</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>8</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B32" t="s">
         <v>18</v>
       </c>
-      <c r="C26" t="str">
-        <f t="shared" si="0"/>
+      <c r="C32" t="str">
+        <f>LEFT(A32,2)</f>
         <v>NL</v>
       </c>
-      <c r="D26">
+      <c r="D32">
         <v>6.1239999999999997</v>
       </c>
-      <c r="E26">
+      <c r="E32">
         <v>52.95</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>11</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-      <c r="C27" t="str">
-        <f t="shared" si="0"/>
+      <c r="C33" t="str">
+        <f>LEFT(A33,2)</f>
         <v>NL</v>
       </c>
-      <c r="D27">
+      <c r="D33">
         <v>5.8019999999999996</v>
       </c>
-      <c r="E27">
+      <c r="E33">
         <v>51.866</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" t="str">
+        <f>LEFT(A34,2)</f>
+        <v>NO</v>
+      </c>
+      <c r="D34">
+        <v>4.8019999999999996</v>
+      </c>
+      <c r="E34">
+        <v>57.234999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="str">
+        <f>LEFT(A35,2)</f>
+        <v>NO</v>
+      </c>
+      <c r="D35">
+        <v>4.1550000000000002</v>
+      </c>
+      <c r="E35">
+        <v>59.642000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" t="str">
+        <f>LEFT(A36,2)</f>
+        <v>NO</v>
+      </c>
+      <c r="D36">
+        <v>7.7690000000000001</v>
+      </c>
+      <c r="E36">
+        <v>64.844999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" t="str">
+        <f>LEFT(A37,2)</f>
+        <v>NO</v>
+      </c>
+      <c r="D37">
+        <v>25.641999999999999</v>
+      </c>
+      <c r="E37">
+        <v>71.424999999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>16</v>
-      </c>
-      <c r="B28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" t="str">
-        <f t="shared" si="0"/>
-        <v>NO</v>
-      </c>
-      <c r="D28">
-        <v>7.5910000000000002</v>
-      </c>
-      <c r="E28">
-        <v>59.381999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" t="str">
-        <f t="shared" si="0"/>
-        <v>UK</v>
-      </c>
-      <c r="D29">
-        <v>1.1679999999999999</v>
-      </c>
-      <c r="E29">
-        <v>53.49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" t="str">
-        <f t="shared" si="0"/>
-        <v>UK</v>
-      </c>
-      <c r="D30">
-        <v>2.0179999999999998</v>
-      </c>
-      <c r="E30">
-        <v>54.834000000000003</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" t="str">
-        <f t="shared" si="0"/>
-        <v>UK</v>
-      </c>
-      <c r="D31">
-        <v>-1.734</v>
-      </c>
-      <c r="E31">
-        <v>56.383000000000003</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" t="str">
-        <f t="shared" si="0"/>
-        <v>UK</v>
-      </c>
-      <c r="D32">
-        <v>-2.7069999999999999</v>
-      </c>
-      <c r="E32">
-        <v>58.180999999999997</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" t="str">
-        <f t="shared" si="0"/>
-        <v>UK</v>
-      </c>
-      <c r="D33">
-        <v>2.1259999999999999</v>
-      </c>
-      <c r="E33">
-        <v>53.896000000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" t="str">
-        <f t="shared" si="0"/>
-        <v>UK</v>
-      </c>
-      <c r="D34">
-        <v>2.8380000000000001</v>
-      </c>
-      <c r="E34">
-        <v>52.908000000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" t="str">
-        <f t="shared" si="0"/>
-        <v>UK</v>
-      </c>
-      <c r="D35">
-        <v>2.2320000000000002</v>
-      </c>
-      <c r="E35">
-        <v>52.11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" t="str">
-        <f t="shared" si="0"/>
-        <v>UK</v>
-      </c>
-      <c r="D36">
-        <v>0.69599999999999995</v>
-      </c>
-      <c r="E36">
-        <v>52.103999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>2</v>
-      </c>
-      <c r="B37" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" t="str">
-        <f t="shared" si="0"/>
-        <v>UK</v>
-      </c>
-      <c r="D37">
-        <v>-1.6639999999999999</v>
-      </c>
-      <c r="E37">
-        <v>53.993000000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>14</v>
       </c>
       <c r="B38" t="s">
         <v>18</v>
       </c>
       <c r="C38" t="str">
-        <f t="shared" si="0"/>
-        <v>UK</v>
+        <f>LEFT(A38,2)</f>
+        <v>NO</v>
       </c>
       <c r="D38">
+        <v>7.5910000000000002</v>
+      </c>
+      <c r="E38">
+        <v>59.381999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" t="str">
+        <f>LEFT(A39,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D39">
+        <v>1.1679999999999999</v>
+      </c>
+      <c r="E39">
+        <v>53.49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" t="str">
+        <f>LEFT(A40,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D40">
+        <v>2.0179999999999998</v>
+      </c>
+      <c r="E40">
+        <v>54.834000000000003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" t="str">
+        <f>LEFT(A41,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D41">
+        <v>-1.734</v>
+      </c>
+      <c r="E41">
+        <v>56.383000000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" t="str">
+        <f>LEFT(A42,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D42">
+        <v>-2.7069999999999999</v>
+      </c>
+      <c r="E42">
+        <v>58.180999999999997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" t="str">
+        <f>LEFT(A43,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D43">
+        <v>1.901</v>
+      </c>
+      <c r="E43">
+        <v>51.755000000000003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" t="str">
+        <f>LEFT(A44,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D44">
+        <v>2.1259999999999999</v>
+      </c>
+      <c r="E44">
+        <v>53.896000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" t="str">
+        <f>LEFT(A45,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D45">
+        <v>1.274</v>
+      </c>
+      <c r="E45">
+        <v>53.226999999999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" t="str">
+        <f>LEFT(A46,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D46">
+        <v>2.8380000000000001</v>
+      </c>
+      <c r="E46">
+        <v>52.908000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" t="str">
+        <f>LEFT(A47,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D47">
+        <v>1.2709999999999999</v>
+      </c>
+      <c r="E47">
+        <v>54.039000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" t="str">
+        <f>LEFT(A48,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D48">
+        <v>2.2320000000000002</v>
+      </c>
+      <c r="E48">
+        <v>52.11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" t="str">
+        <f>LEFT(A49,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D49">
+        <v>-0.41799999999999998</v>
+      </c>
+      <c r="E49">
+        <v>57.009</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" t="str">
+        <f>LEFT(A50,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D50">
+        <v>-1.294</v>
+      </c>
+      <c r="E50">
+        <v>58.362000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" t="str">
+        <f>LEFT(A51,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D51">
+        <v>-5.0750000000000002</v>
+      </c>
+      <c r="E51">
+        <v>58.83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>46</v>
+      </c>
+      <c r="B52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" t="str">
+        <f>LEFT(A52,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D52">
+        <v>-0.18099999999999999</v>
+      </c>
+      <c r="E52">
+        <v>60.304000000000002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" t="str">
+        <f>LEFT(A53,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D53">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="E53">
+        <v>52.103999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" t="str">
+        <f>LEFT(A54,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D54">
+        <v>-1.6639999999999999</v>
+      </c>
+      <c r="E54">
+        <v>53.993000000000002</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" t="str">
+        <f>LEFT(A55,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D55">
         <v>-4.5810000000000004</v>
       </c>
-      <c r="E38">
+      <c r="E55">
         <v>56.476999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>6</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B56" t="s">
         <v>18</v>
       </c>
-      <c r="C39" t="str">
-        <f t="shared" si="0"/>
-        <v>UK</v>
-      </c>
-      <c r="D39">
+      <c r="C56" t="str">
+        <f>LEFT(A56,2)</f>
+        <v>UK</v>
+      </c>
+      <c r="D56">
         <v>-2.4449999999999998</v>
       </c>
-      <c r="E39">
+      <c r="E56">
         <v>51.76</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E28" xr:uid="{AB4994A1-993F-4B0E-B5C8-90E717560862}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E39">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E56">
       <sortCondition ref="A1:A28"/>
     </sortState>
   </autoFilter>
